--- a/WorkBot/main/data/transfer_archive/Bakery_Easthill_20260403.xlsx
+++ b/WorkBot/main/data/transfer_archive/Bakery_Easthill_20260403.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\main\data\transfers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2468A5D0-7BB7-438C-9082-3899B4670794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8996744-7F7F-4D57-AF09-06EB81DA524A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Name</t>
   </si>
@@ -28,12 +28,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Long Sleeve Shirt - Dog w/ Baguette</t>
-  </si>
-  <si>
-    <t>Mug - Stoneware Pottery (java taster)</t>
-  </si>
-  <si>
     <t>FRZ Fruit - Mango</t>
   </si>
   <si>
@@ -43,9 +37,6 @@
     <t>Sweet Street - Bar Lemon Luscious Sliced</t>
   </si>
   <si>
-    <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
-  </si>
-  <si>
     <t>Sweet Street - Pie Oreo Cookie Bash Sliced</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
   </si>
   <si>
     <t>Peanut Butter - Chunky</t>
-  </si>
-  <si>
-    <t>Peanut Butter - Creamy</t>
   </si>
   <si>
     <t>Red Bull</t>
@@ -536,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.140625" bestFit="1" customWidth="1"/>
@@ -553,7 +541,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -561,7 +549,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -569,7 +557,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -577,7 +565,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -585,7 +573,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -593,7 +581,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -601,7 +589,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -609,7 +597,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -617,7 +605,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -625,7 +613,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -633,7 +621,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -641,7 +629,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -649,7 +637,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -657,7 +645,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -665,7 +653,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -673,7 +661,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -681,7 +669,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -689,7 +677,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -697,7 +685,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -705,7 +693,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -713,7 +701,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -721,7 +709,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -729,7 +717,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -737,7 +725,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -745,7 +733,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -753,7 +741,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -761,7 +749,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -769,7 +757,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -777,7 +765,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -785,7 +773,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -793,7 +781,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -801,7 +789,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -809,7 +797,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -817,7 +805,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -825,15 +813,15 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -841,39 +829,39 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -881,7 +869,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -889,15 +877,15 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -905,50 +893,50 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -956,7 +944,7 @@
         <v>48</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -964,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -975,41 +963,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B58">
-    <sortCondition ref="A2:A58"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B54">
+    <sortCondition ref="A2:A54"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
